--- a/sheets/대금율보/검수/열두줄.xlsx
+++ b/sheets/대금율보/검수/열두줄.xlsx
@@ -4725,8 +4725,7 @@
       <c r="B3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△
-淋淋
-‹</t>
+淋淋</t>
         </is>
       </c>
       <c r="C3" s="22" t="inlineStr">
@@ -4749,7 +4748,7 @@
       </c>
       <c r="H3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋‹
+          <t xml:space="preserve">淋
 太林</t>
         </is>
       </c>
@@ -4786,11 +4785,7 @@
           <t xml:space="preserve">누가</t>
         </is>
       </c>
-      <c r="D4" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="D4" s="21"/>
       <c r="E4" s="23"/>
       <c r="F4" s="21" t="inlineStr">
         <is>
@@ -4804,7 +4799,7 @@
       </c>
       <c r="H4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–林‹
+          <t xml:space="preserve">–林
 林</t>
         </is>
       </c>
@@ -4833,8 +4828,7 @@
       <c r="B5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
-–汰
-‹</t>
+–汰</t>
         </is>
       </c>
       <c r="C5" s="23" t="inlineStr">
@@ -4854,7 +4848,7 @@
       </c>
       <c r="F5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林‹
+          <t xml:space="preserve">林
 –汰</t>
         </is>
       </c>
@@ -4918,7 +4912,7 @@
       <c r="G6" s="24"/>
       <c r="H6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–南‹
+          <t xml:space="preserve">–南
 林</t>
         </is>
       </c>
@@ -5003,11 +4997,7 @@
     </row>
     <row r="8" ht="56" customHeight="1">
       <c r="A8" s="0"/>
-      <c r="B8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="B8" s="21"/>
       <c r="C8" s="23"/>
       <c r="D8" s="21"/>
       <c r="E8" s="23"/>
@@ -5069,7 +5059,7 @@
       </c>
       <c r="F9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰‹
+          <t xml:space="preserve">汰
 –淋</t>
         </is>
       </c>
@@ -5111,8 +5101,7 @@
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林ㅅ
-‹</t>
+          <t xml:space="preserve">林ㅅ</t>
         </is>
       </c>
       <c r="C10" s="24"/>
@@ -5282,14 +5271,14 @@
       <c r="E13" s="26"/>
       <c r="F13" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰‹
+          <t xml:space="preserve">汰
 –淋</t>
         </is>
       </c>
       <c r="G13" s="23"/>
       <c r="H13" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰‹
+          <t xml:space="preserve">汰
 –淋</t>
         </is>
       </c>
@@ -5317,17 +5306,9 @@
     </row>
     <row r="14" ht="56" customHeight="1">
       <c r="A14" s="0"/>
-      <c r="B14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="B14" s="21"/>
       <c r="C14" s="24"/>
-      <c r="D14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="D14" s="21"/>
       <c r="E14" s="24"/>
       <c r="F14" s="21" t="inlineStr">
         <is>
@@ -5397,8 +5378,7 @@
       <c r="J15" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△
-無汰
-‹</t>
+無汰</t>
         </is>
       </c>
       <c r="K15" s="22" t="inlineStr">
@@ -5409,8 +5389,7 @@
       <c r="L15" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無南
-汰
-‹</t>
+汰</t>
         </is>
       </c>
       <c r="M15" s="22"/>
@@ -5436,8 +5415,7 @@
       </c>
       <c r="F16" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林ㅅ
-‹</t>
+          <t xml:space="preserve">林ㅅ</t>
         </is>
       </c>
       <c r="G16" s="23"/>
@@ -5504,7 +5482,7 @@
       <c r="H17" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△太
-–林‹</t>
+–林</t>
         </is>
       </c>
       <c r="I17" s="23" t="inlineStr">
@@ -5515,8 +5493,7 @@
       <c r="J17" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">林林
-–無
-‹</t>
+–無</t>
         </is>
       </c>
       <c r="K17" s="23" t="inlineStr">
@@ -5558,7 +5535,7 @@
       </c>
       <c r="J18" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南林‹
+          <t xml:space="preserve">南林
 –夾</t>
         </is>
       </c>
@@ -5688,7 +5665,7 @@
       </c>
       <c r="H21" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林‹
+          <t xml:space="preserve">林
 –汰</t>
         </is>
       </c>

--- a/sheets/대금율보/검수/열두줄.xlsx
+++ b/sheets/대금율보/검수/열두줄.xlsx
@@ -4684,24 +4684,24 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="15.29" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="15.29" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="15.29" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="15.29" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="15.29" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="15.29" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="76.92" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -4720,7 +4720,7 @@
       <c r="L2" s="20"/>
       <c r="M2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="68.77" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -4772,7 +4772,7 @@
       </c>
       <c r="M3" s="22"/>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="68.77" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -4823,7 +4823,7 @@
       </c>
       <c r="M4" s="23"/>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="68.77" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -4879,7 +4879,7 @@
       </c>
       <c r="M5" s="23"/>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="68.77" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -4936,7 +4936,7 @@
       </c>
       <c r="M6" s="24"/>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="68.77" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -4995,7 +4995,7 @@
       </c>
       <c r="M7" s="22"/>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="68.77" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21"/>
       <c r="C8" s="23"/>
@@ -5037,7 +5037,7 @@
       </c>
       <c r="M8" s="23"/>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="68.77" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -5097,7 +5097,7 @@
       </c>
       <c r="M9" s="23"/>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="68.77" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="M10" s="24"/>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="68.77" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -5199,7 +5199,7 @@
       </c>
       <c r="M11" s="22"/>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="68.77" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -5255,7 +5255,7 @@
       </c>
       <c r="M12" s="23"/>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="68.77" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
@@ -5304,7 +5304,7 @@
       </c>
       <c r="M13" s="23"/>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="68.77" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21"/>
       <c r="C14" s="24"/>
@@ -5338,7 +5338,7 @@
       </c>
       <c r="M14" s="24"/>
     </row>
-    <row r="15" ht="56" customHeight="1">
+    <row r="15" ht="68.77" customHeight="true">
       <c r="A15" s="0"/>
       <c r="B15" s="21" t="inlineStr">
         <is>
@@ -5394,7 +5394,7 @@
       </c>
       <c r="M15" s="22"/>
     </row>
-    <row r="16" ht="56" customHeight="1">
+    <row r="16" ht="68.77" customHeight="true">
       <c r="A16" s="0"/>
       <c r="B16" s="21" t="inlineStr">
         <is>
@@ -5448,7 +5448,7 @@
       </c>
       <c r="M16" s="23"/>
     </row>
-    <row r="17" ht="56" customHeight="1">
+    <row r="17" ht="68.77" customHeight="true">
       <c r="A17" s="0"/>
       <c r="B17" s="21" t="inlineStr">
         <is>
@@ -5509,7 +5509,7 @@
       </c>
       <c r="M17" s="23"/>
     </row>
-    <row r="18" ht="56" customHeight="1">
+    <row r="18" ht="68.77" customHeight="true">
       <c r="A18" s="0"/>
       <c r="B18" s="21" t="inlineStr">
         <is>
@@ -5552,7 +5552,7 @@
       </c>
       <c r="M18" s="24"/>
     </row>
-    <row r="19" ht="56" customHeight="1">
+    <row r="19" ht="68.77" customHeight="true">
       <c r="A19" s="0"/>
       <c r="B19" s="21" t="inlineStr">
         <is>
@@ -5604,7 +5604,7 @@
       </c>
       <c r="M19" s="22"/>
     </row>
-    <row r="20" ht="56" customHeight="1">
+    <row r="20" ht="68.77" customHeight="true">
       <c r="A20" s="0"/>
       <c r="B20" s="21"/>
       <c r="C20" s="23"/>
@@ -5638,7 +5638,7 @@
       </c>
       <c r="M20" s="23"/>
     </row>
-    <row r="21" ht="56" customHeight="1">
+    <row r="21" ht="68.77" customHeight="true">
       <c r="A21" s="0"/>
       <c r="B21" s="21"/>
       <c r="C21" s="23"/>
@@ -5688,7 +5688,7 @@
       </c>
       <c r="M21" s="23"/>
     </row>
-    <row r="22" ht="56" customHeight="1">
+    <row r="22" ht="68.77" customHeight="true">
       <c r="A22" s="0"/>
       <c r="B22" s="21" t="inlineStr">
         <is>
@@ -5740,6 +5740,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="62"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="52"/>
 </worksheet>
 </file>